--- a/xls/Tabelas.xlsx
+++ b/xls/Tabelas.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_979C499F50A2988B1A65E97A360954C7598ED132" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA08B937-174C-41B6-B7F5-CBB3F135D447}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="90" windowWidth="20730" windowHeight="10455"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal Padrão" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,20 @@
     <sheet name="t-student" sheetId="3" r:id="rId3"/>
     <sheet name="F Snedecor" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -663,29 +677,29 @@
     <t>z</t>
   </si>
   <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
-  </si>
-  <si>
     <t>P(Z &gt; ztab) =</t>
   </si>
   <si>
     <t>ztab =</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,13 +771,6 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -859,7 +866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -875,7 +882,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -886,7 +892,6 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -922,7 +927,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2061" name="Imagem 3"/>
+        <xdr:cNvPr id="2061" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D080000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -995,7 +1006,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3085" name="Imagem 11"/>
+        <xdr:cNvPr id="3085" name="Imagem 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D0C0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1068,7 +1085,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4109" name="Imagem 3"/>
+        <xdr:cNvPr id="4109" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000D100000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1141,7 +1164,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1037" name="Imagem 25"/>
+        <xdr:cNvPr id="1037" name="Imagem 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000D040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1198,9 +1227,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1238,9 +1267,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1275,7 +1304,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1310,7 +1339,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1483,7 +1512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:O36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1491,42 +1520,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>0</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>0.01</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="12">
         <v>0.02</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>0.03</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="12">
         <v>0.04</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <v>0.05</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="12">
         <v>0.06</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="12">
         <v>0.08</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="12">
         <v>0.09</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>0</v>
       </c>
       <c r="F3" s="3">
@@ -1571,7 +1600,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>0.1</v>
       </c>
       <c r="F4" s="3">
@@ -1616,7 +1645,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>0.2</v>
       </c>
       <c r="F5" s="3">
@@ -1661,7 +1690,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>0.3</v>
       </c>
       <c r="F6" s="3">
@@ -1706,52 +1735,52 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <v>0.4</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="15">
         <f t="shared" si="0"/>
         <v>0.34457825838967571</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f t="shared" si="2"/>
         <v>0.34090297377232259</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <f t="shared" si="2"/>
         <v>0.33724272684824941</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <f t="shared" si="2"/>
         <v>0.33359782059545762</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <f t="shared" si="2"/>
         <v>0.32996855366059363</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <f t="shared" si="2"/>
         <v>0.32635522028791997</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <f t="shared" si="2"/>
         <v>0.32275811025034773</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <f t="shared" si="2"/>
         <v>0.3191775087825558</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <f t="shared" si="2"/>
         <v>0.31561369651622251</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <f t="shared" si="2"/>
         <v>0.31206694941739055</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>0.5</v>
       </c>
       <c r="F8" s="3">
@@ -1797,12 +1826,12 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>0.6</v>
       </c>
       <c r="F9" s="3">
@@ -1848,13 +1877,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="3">
         <f>NORMSINV(1-B9)</f>
         <v>1.9599639845400536</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>0.7</v>
       </c>
       <c r="F10" s="3">
@@ -1899,7 +1928,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>0.8</v>
       </c>
       <c r="F11" s="3">
@@ -1945,58 +1974,58 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <v>0.9</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <f t="shared" si="0"/>
         <v>0.18406012534675953</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f t="shared" si="2"/>
         <v>0.18141125489179721</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <f t="shared" si="2"/>
         <v>0.17878637961437172</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <f t="shared" si="2"/>
         <v>0.17618554224525784</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f t="shared" si="2"/>
         <v>0.17360878033862448</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <f t="shared" si="2"/>
         <v>0.17105612630848177</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="10">
         <f t="shared" si="2"/>
         <v>0.16852760746683781</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <f t="shared" si="2"/>
         <v>0.16602324606352958</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="10">
         <f t="shared" si="2"/>
         <v>0.16354305932769231</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="10">
         <f t="shared" si="2"/>
         <v>0.16108705951083091</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3">
         <v>1.96</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <v>1</v>
       </c>
       <c r="F13" s="3">
@@ -2042,13 +2071,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3">
         <f>1-NORMSDIST(B13)</f>
         <v>2.4997895148220484E-2</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>1.1000000000000001</v>
       </c>
       <c r="F14" s="3">
@@ -2093,7 +2122,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>1.2</v>
       </c>
       <c r="F15" s="3">
@@ -2138,7 +2167,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E16" s="14">
+      <c r="E16" s="13">
         <v>1.3</v>
       </c>
       <c r="F16" s="3">
@@ -2183,52 +2212,52 @@
       </c>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <v>1.4</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <f t="shared" si="0"/>
         <v>8.0756659233771066E-2</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <f t="shared" si="3"/>
         <v>7.9269841453392442E-2</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <f t="shared" si="3"/>
         <v>7.780384052654632E-2</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <f t="shared" si="3"/>
         <v>7.6358509536739172E-2</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <f t="shared" si="3"/>
         <v>7.4933699534327047E-2</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <f t="shared" si="3"/>
         <v>7.3529259609648401E-2</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="10">
         <f t="shared" si="3"/>
         <v>7.2145036965893805E-2</v>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="10">
         <f t="shared" si="3"/>
         <v>7.078087699168556E-2</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="10">
         <f t="shared" si="3"/>
         <v>6.9436623333331671E-2</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="10">
         <f t="shared" si="3"/>
         <v>6.8112117966725449E-2</v>
       </c>
     </row>
     <row r="18" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E18" s="14">
+      <c r="E18" s="13">
         <v>1.5</v>
       </c>
       <c r="F18" s="3">
@@ -2273,7 +2302,7 @@
       </c>
     </row>
     <row r="19" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>1.6</v>
       </c>
       <c r="F19" s="3">
@@ -2318,7 +2347,7 @@
       </c>
     </row>
     <row r="20" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E20" s="14">
+      <c r="E20" s="13">
         <v>1.7</v>
       </c>
       <c r="F20" s="3">
@@ -2363,7 +2392,7 @@
       </c>
     </row>
     <row r="21" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E21" s="14">
+      <c r="E21" s="13">
         <v>1.8</v>
       </c>
       <c r="F21" s="3">
@@ -2408,52 +2437,52 @@
       </c>
     </row>
     <row r="22" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E22" s="15">
+      <c r="E22" s="14">
         <v>1.9</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="15">
         <f t="shared" si="0"/>
         <v>2.8716559816001852E-2</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="10">
         <f t="shared" si="3"/>
         <v>2.8066606659772564E-2</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="10">
         <f t="shared" si="3"/>
         <v>2.7428949703836802E-2</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="10">
         <f t="shared" si="3"/>
         <v>2.6803418877054952E-2</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="10">
         <f t="shared" si="3"/>
         <v>2.6189844940452733E-2</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="10">
         <f t="shared" si="3"/>
         <v>2.5588059521638562E-2</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="10">
         <f t="shared" si="3"/>
         <v>2.4997895148220484E-2</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="10">
         <f t="shared" si="3"/>
         <v>2.4419185280222577E-2</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="10">
         <f t="shared" si="3"/>
         <v>2.3851764341508486E-2</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="10">
         <f t="shared" si="3"/>
         <v>2.3295467750211851E-2</v>
       </c>
     </row>
     <row r="23" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E23" s="14">
+      <c r="E23" s="13">
         <v>2</v>
       </c>
       <c r="F23" s="3">
@@ -2498,7 +2527,7 @@
       </c>
     </row>
     <row r="24" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E24" s="14">
+      <c r="E24" s="13">
         <v>2.1</v>
       </c>
       <c r="F24" s="3">
@@ -2543,7 +2572,7 @@
       </c>
     </row>
     <row r="25" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E25" s="14">
+      <c r="E25" s="13">
         <v>2.2000000000000002</v>
       </c>
       <c r="F25" s="3">
@@ -2588,7 +2617,7 @@
       </c>
     </row>
     <row r="26" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E26" s="14">
+      <c r="E26" s="13">
         <v>2.2999999999999998</v>
       </c>
       <c r="F26" s="3">
@@ -2633,52 +2662,52 @@
       </c>
     </row>
     <row r="27" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <v>2.4</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="15">
         <f t="shared" si="0"/>
         <v>8.1975359245961554E-3</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="10">
         <f t="shared" si="4"/>
         <v>7.9762602607337252E-3</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="10">
         <f t="shared" si="4"/>
         <v>7.760253550553653E-3</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="10">
         <f t="shared" si="4"/>
         <v>7.5494114163091597E-3</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="10">
         <f t="shared" si="4"/>
         <v>7.3436309553482904E-3</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="10">
         <f t="shared" si="4"/>
         <v>7.1428107352714543E-3</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="10">
         <f t="shared" si="4"/>
         <v>6.9468507886243369E-3</v>
       </c>
-      <c r="M27" s="11">
+      <c r="M27" s="10">
         <f t="shared" si="4"/>
         <v>6.7556526071406164E-3</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="10">
         <f t="shared" si="4"/>
         <v>6.5691191355468082E-3</v>
       </c>
-      <c r="O27" s="11">
+      <c r="O27" s="10">
         <f t="shared" si="4"/>
         <v>6.3871547649432259E-3</v>
       </c>
     </row>
     <row r="28" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E28" s="14">
+      <c r="E28" s="13">
         <v>2.5</v>
       </c>
       <c r="F28" s="3">
@@ -2723,7 +2752,7 @@
       </c>
     </row>
     <row r="29" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E29" s="14">
+      <c r="E29" s="13">
         <v>2.6</v>
       </c>
       <c r="F29" s="3">
@@ -2768,7 +2797,7 @@
       </c>
     </row>
     <row r="30" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E30" s="14">
+      <c r="E30" s="13">
         <v>2.7</v>
       </c>
       <c r="F30" s="3">
@@ -2813,7 +2842,7 @@
       </c>
     </row>
     <row r="31" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E31" s="14">
+      <c r="E31" s="13">
         <v>2.8</v>
       </c>
       <c r="F31" s="3">
@@ -2858,52 +2887,52 @@
       </c>
     </row>
     <row r="32" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E32" s="15">
+      <c r="E32" s="14">
         <v>2.9</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="15">
         <f t="shared" si="0"/>
         <v>1.8658133003840449E-3</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="10">
         <f t="shared" si="4"/>
         <v>1.8071437808064861E-3</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="10">
         <f t="shared" si="4"/>
         <v>1.7501569286760832E-3</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="10">
         <f t="shared" si="4"/>
         <v>1.694810019277293E-3</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="10">
         <f t="shared" si="4"/>
         <v>1.6410612341569708E-3</v>
       </c>
-      <c r="K32" s="11">
+      <c r="K32" s="10">
         <f t="shared" si="4"/>
         <v>1.5888696473648212E-3</v>
       </c>
-      <c r="L32" s="11">
+      <c r="L32" s="10">
         <f t="shared" si="4"/>
         <v>1.538195211738036E-3</v>
       </c>
-      <c r="M32" s="11">
+      <c r="M32" s="10">
         <f t="shared" si="4"/>
         <v>1.4889987452374465E-3</v>
       </c>
-      <c r="N32" s="11">
+      <c r="N32" s="10">
         <f t="shared" si="4"/>
         <v>1.4412419173399638E-3</v>
       </c>
-      <c r="O32" s="11">
+      <c r="O32" s="10">
         <f t="shared" si="4"/>
         <v>1.3948872354923036E-3</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E33" s="14">
+      <c r="E33" s="13">
         <v>3</v>
       </c>
       <c r="F33" s="3">
@@ -2947,14 +2976,14 @@
         <v>1.0007824766140594E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>16</v>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +2994,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4177,7 +4206,7 @@
       </c>
     </row>
     <row r="28" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E28" s="9">
+      <c r="E28" s="5">
         <v>26</v>
       </c>
       <c r="F28" s="7">
@@ -4222,7 +4251,7 @@
       </c>
     </row>
     <row r="29" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E29" s="9">
+      <c r="E29" s="5">
         <v>27</v>
       </c>
       <c r="F29" s="7">
@@ -4267,7 +4296,7 @@
       </c>
     </row>
     <row r="30" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E30" s="9">
+      <c r="E30" s="5">
         <v>28</v>
       </c>
       <c r="F30" s="7">
@@ -4312,7 +4341,7 @@
       </c>
     </row>
     <row r="31" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E31" s="9">
+      <c r="E31" s="5">
         <v>29</v>
       </c>
       <c r="F31" s="7">
@@ -4537,7 +4566,7 @@
       </c>
     </row>
     <row r="36" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E36" s="9">
+      <c r="E36" s="5">
         <v>70</v>
       </c>
       <c r="F36" s="7">
@@ -4582,7 +4611,7 @@
       </c>
     </row>
     <row r="37" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <v>80</v>
       </c>
       <c r="F37" s="7">
@@ -4627,7 +4656,7 @@
       </c>
     </row>
     <row r="38" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E38" s="9">
+      <c r="E38" s="5">
         <v>90</v>
       </c>
       <c r="F38" s="7">
@@ -4672,7 +4701,7 @@
       </c>
     </row>
     <row r="39" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E39" s="9">
+      <c r="E39" s="5">
         <v>100</v>
       </c>
       <c r="F39" s="7">
@@ -4723,7 +4752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5420,7 +5449,7 @@
       </c>
     </row>
     <row r="28" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E28" s="9">
+      <c r="E28" s="5">
         <v>26</v>
       </c>
       <c r="F28" s="7">
@@ -5445,7 +5474,7 @@
       </c>
     </row>
     <row r="29" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E29" s="9">
+      <c r="E29" s="5">
         <v>27</v>
       </c>
       <c r="F29" s="7">
@@ -5470,7 +5499,7 @@
       </c>
     </row>
     <row r="30" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E30" s="9">
+      <c r="E30" s="5">
         <v>28</v>
       </c>
       <c r="F30" s="7">
@@ -5495,7 +5524,7 @@
       </c>
     </row>
     <row r="31" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E31" s="9">
+      <c r="E31" s="5">
         <v>29</v>
       </c>
       <c r="F31" s="7">
@@ -5620,7 +5649,7 @@
       </c>
     </row>
     <row r="36" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E36" s="9">
+      <c r="E36" s="5">
         <v>120</v>
       </c>
       <c r="F36" s="7">
@@ -5645,7 +5674,7 @@
       </c>
     </row>
     <row r="37" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F37" s="7">
@@ -5676,7 +5705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5754,79 +5783,79 @@
       </c>
       <c r="E3" s="7">
         <f>FINV($B$9,E$2,$D3)</f>
-        <v>647.78901147784529</v>
+        <v>1.5437125086741339E-3</v>
       </c>
       <c r="F3" s="7">
         <f t="shared" ref="F3:W3" si="0">FINV($B$9,F$2,$D3)</f>
-        <v>799.5</v>
+        <v>2.5969756738987534E-2</v>
       </c>
       <c r="G3" s="7">
         <f t="shared" si="0"/>
-        <v>864.16297216352962</v>
+        <v>5.7328130783207677E-2</v>
       </c>
       <c r="H3" s="7">
         <f t="shared" si="0"/>
-        <v>899.58331017803755</v>
+        <v>8.1847376258202265E-2</v>
       </c>
       <c r="I3" s="7">
         <f t="shared" si="0"/>
-        <v>921.84790329970929</v>
+        <v>9.9930226750918491E-2</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" si="0"/>
-        <v>937.11108344820218</v>
+        <v>0.11346744376739329</v>
       </c>
       <c r="K3" s="7">
         <f t="shared" si="0"/>
-        <v>948.21688909393424</v>
+        <v>0.12387476989929583</v>
       </c>
       <c r="L3" s="7">
         <f t="shared" si="0"/>
-        <v>956.65622060310352</v>
+        <v>0.13208500500103093</v>
       </c>
       <c r="M3" s="7">
         <f t="shared" si="0"/>
-        <v>963.28457894676114</v>
+        <v>0.13871004448933549</v>
       </c>
       <c r="N3" s="7">
         <f t="shared" si="0"/>
-        <v>968.62744367696587</v>
+        <v>0.14416018272975339</v>
       </c>
       <c r="O3" s="7">
         <f t="shared" si="0"/>
-        <v>973.02520095986279</v>
+        <v>0.14871813164358721</v>
       </c>
       <c r="P3" s="7">
         <f t="shared" si="0"/>
-        <v>976.70794987733063</v>
+        <v>0.15258396163907764</v>
       </c>
       <c r="Q3" s="7">
         <f t="shared" si="0"/>
-        <v>984.86684125760485</v>
+        <v>0.16130330651336097</v>
       </c>
       <c r="R3" s="7">
         <f t="shared" si="0"/>
-        <v>993.10280457625004</v>
+        <v>0.17031441058889954</v>
       </c>
       <c r="S3" s="7">
         <f t="shared" si="0"/>
-        <v>998.08078617845013</v>
+        <v>0.17585924533377451</v>
       </c>
       <c r="T3" s="7">
         <f>FINV($B$9,T$2,$D3)</f>
-        <v>1001.4144080879453</v>
+        <v>0.17961270124511292</v>
       </c>
       <c r="U3" s="7">
         <f t="shared" si="0"/>
-        <v>1005.5980971657891</v>
+        <v>0.18436791799964874</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" si="0"/>
-        <v>1008.1171192761956</v>
+        <v>0.18725458352531049</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" si="0"/>
-        <v>1013.1747740293274</v>
+        <v>0.19310261016007935</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -5835,79 +5864,79 @@
       </c>
       <c r="E4" s="3">
         <f t="shared" ref="E4:S31" si="1">FINV($B$9,E$2,$D4)</f>
-        <v>38.506329113924046</v>
+        <v>1.250781738586619E-3</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="1"/>
-        <v>38.999999999999993</v>
+        <v>2.5641025641025668E-2</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="1"/>
-        <v>39.165494564013635</v>
+        <v>6.2328182900557548E-2</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="1"/>
-        <v>39.248417658131501</v>
+        <v>9.3904555388932859E-2</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="1"/>
-        <v>39.298227775403326</v>
+        <v>0.1185730341565321</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="1"/>
-        <v>39.331457962410276</v>
+        <v>0.13774378501029799</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="1"/>
-        <v>39.355205292186163</v>
+        <v>0.15286966249175854</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="1"/>
-        <v>39.37302206870244</v>
+        <v>0.16503100484002348</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="1"/>
-        <v>39.386883282551338</v>
+        <v>0.17498714848586769</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="1"/>
-        <v>39.397974597864426</v>
+        <v>0.18327117146309196</v>
       </c>
       <c r="O4" s="3">
         <f t="shared" si="1"/>
-        <v>39.407050860300984</v>
+        <v>0.19026275871752654</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" si="1"/>
-        <v>39.41461547789347</v>
+        <v>0.19623745428736289</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" si="1"/>
-        <v>39.43126104639709</v>
+        <v>0.20986146213486329</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" si="1"/>
-        <v>39.447911303378291</v>
+        <v>0.22415214750975593</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
-        <v>39.457903708037207</v>
+        <v>0.23304958327740055</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" ref="T4:W31" si="2">FINV($B$9,T$2,$D4)</f>
-        <v>39.464566248839333</v>
+        <v>0.23911657381363116</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="2"/>
-        <v>39.472895479750406</v>
+        <v>0.24685311184391137</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="2"/>
-        <v>39.477893580914909</v>
+        <v>0.25157670288763634</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="2"/>
-        <v>39.48789104913412</v>
+        <v>0.26120798217669927</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -5916,79 +5945,79 @@
       </c>
       <c r="E5" s="3">
         <f t="shared" si="1"/>
-        <v>17.443443320725127</v>
+        <v>1.1571891323882912E-3</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="1"/>
-        <v>16.044106429277196</v>
+        <v>2.5532678985211364E-2</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="1"/>
-        <v>15.439182378747292</v>
+        <v>6.4770269271288886E-2</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>15.100978932045942</v>
+        <v>0.10020844828057998</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="1"/>
-        <v>14.884822920641971</v>
+        <v>0.12880639842126201</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
-        <v>14.734718413039163</v>
+        <v>0.15154273867775422</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="1"/>
-        <v>14.624395022241272</v>
+        <v>0.16978449959353234</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="1"/>
-        <v>14.53988657041725</v>
+        <v>0.18463939320545528</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="1"/>
-        <v>14.473080651773735</v>
+        <v>0.19692332308169183</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="1"/>
-        <v>14.418942042127425</v>
+        <v>0.20722719371309561</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="1"/>
-        <v>14.374179860495522</v>
+        <v>0.21598155695577409</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="1"/>
-        <v>14.336552351194756</v>
+        <v>0.22350440192946905</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="1"/>
-        <v>14.252711453674936</v>
+        <v>0.24080115333177904</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="1"/>
-        <v>14.167381381400022</v>
+        <v>0.25915472714686333</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="1"/>
-        <v>14.115452441308326</v>
+        <v>0.27068923772131681</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="2"/>
-        <v>14.080523373263894</v>
+        <v>0.27860126737665974</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="2"/>
-        <v>14.036509073627915</v>
+        <v>0.2887453146190927</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" si="2"/>
-        <v>14.009910324346327</v>
+        <v>0.29496882468828572</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" si="2"/>
-        <v>13.956279860799276</v>
+        <v>0.30772839736703939</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -5997,79 +6026,79 @@
       </c>
       <c r="E6" s="3">
         <f t="shared" si="1"/>
-        <v>12.217862633071109</v>
+        <v>1.1116257812765452E-3</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" si="1"/>
-        <v>10.649110640673515</v>
+        <v>2.5478734167333251E-2</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="1"/>
-        <v>9.9791985322438865</v>
+        <v>6.6220872467935885E-2</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="1"/>
-        <v>9.6045298847228668</v>
+        <v>0.1041175374539277</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>9.3644708158082981</v>
+        <v>0.13535672229749915</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
-        <v>9.1973110793662123</v>
+        <v>0.16058681855284121</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="1"/>
-        <v>9.0741410515680592</v>
+        <v>0.18107431715485356</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="1"/>
-        <v>8.979580415011041</v>
+        <v>0.19791664165926665</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="1"/>
-        <v>8.9046816145985854</v>
+        <v>0.21195069324827034</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" si="1"/>
-        <v>8.8438809735214274</v>
+        <v>0.22379667769203448</v>
       </c>
       <c r="O6" s="3">
         <f t="shared" si="1"/>
-        <v>8.7935354532957088</v>
+        <v>0.23391421113436284</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="1"/>
-        <v>8.7511589241360781</v>
+        <v>0.2426472650535908</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="1"/>
-        <v>8.656541174913869</v>
+        <v>0.26286242755651257</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="1"/>
-        <v>8.5599431870535465</v>
+        <v>0.28451969625651358</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
-        <v>8.5009963328379978</v>
+        <v>0.2982395602192644</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="2"/>
-        <v>8.4612740138555278</v>
+        <v>0.30769937260591501</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="2"/>
-        <v>8.4111323894286567</v>
+        <v>0.31988594984994734</v>
       </c>
       <c r="V6" s="3">
         <f t="shared" si="2"/>
-        <v>8.3807817877216593</v>
+        <v>0.32739493765419087</v>
       </c>
       <c r="W6" s="3">
         <f t="shared" si="2"/>
-        <v>8.3194693977786489</v>
+        <v>0.34286709420193623</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -6078,79 +6107,79 @@
       </c>
       <c r="E7" s="3">
         <f t="shared" si="1"/>
-        <v>10.006982196613588</v>
+        <v>1.0847776476146998E-3</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="1"/>
-        <v>8.4336207394327811</v>
+        <v>2.5446440122317643E-2</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="1"/>
-        <v>7.7635894820185474</v>
+        <v>6.7182525807090429E-2</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>7.3878857512677536</v>
+        <v>0.10678660008335832</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="1"/>
-        <v>7.1463818287328316</v>
+        <v>0.13993095022986143</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="1"/>
-        <v>6.9777018585355677</v>
+        <v>0.16701279718024784</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="1"/>
-        <v>6.8530756285766561</v>
+        <v>0.18920627932036413</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="1"/>
-        <v>6.7571720073946775</v>
+        <v>0.2075862151806841</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="1"/>
-        <v>6.6810543464609058</v>
+        <v>0.22299470988239012</v>
       </c>
       <c r="N7" s="3">
         <f t="shared" si="1"/>
-        <v>6.6191543314249648</v>
+        <v>0.23606699163560677</v>
       </c>
       <c r="O7" s="3">
         <f t="shared" si="1"/>
-        <v>6.5678185908290319</v>
+        <v>0.24728002958627771</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="1"/>
-        <v>6.5245492185635907</v>
+        <v>0.25699449491760568</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="1"/>
-        <v>6.4277281670787856</v>
+        <v>0.27960958175665523</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="1"/>
-        <v>6.3285552351325691</v>
+        <v>0.30403861987120806</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
-        <v>6.2678602652813593</v>
+        <v>0.31962315319182616</v>
       </c>
       <c r="T7" s="3">
         <f t="shared" si="2"/>
-        <v>6.2268789025067681</v>
+        <v>0.33041833768744405</v>
       </c>
       <c r="U7" s="3">
         <f t="shared" si="2"/>
-        <v>6.1750497039750165</v>
+        <v>0.34438554711038011</v>
       </c>
       <c r="V7" s="3">
         <f t="shared" si="2"/>
-        <v>6.1436219916871657</v>
+        <v>0.35302581013179507</v>
       </c>
       <c r="W7" s="3">
         <f t="shared" si="2"/>
-        <v>6.0799990529765431</v>
+        <v>0.37091176994150926</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -6159,79 +6188,79 @@
       </c>
       <c r="E8" s="3">
         <f t="shared" si="1"/>
-        <v>8.8131006286700746</v>
+        <v>1.0671093509217638E-3</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>7.2598556800601788</v>
+        <v>2.5424941047334615E-2</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="1"/>
-        <v>6.5987985219564722</v>
+        <v>6.7866923002415383E-2</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>6.2271611643576446</v>
+        <v>0.10872743037293356</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="1"/>
-        <v>5.9875651260469276</v>
+        <v>0.14331366118441086</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="1"/>
-        <v>5.819756578960777</v>
+        <v>0.17182849255502167</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="1"/>
-        <v>5.6954704736831747</v>
+        <v>0.1953660496287597</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="1"/>
-        <v>5.5996230050430462</v>
+        <v>0.21497537660866212</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="1"/>
-        <v>5.5234066239755757</v>
+        <v>0.23149638763607783</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="1"/>
-        <v>5.4613237187317791</v>
+        <v>0.2455716485129355</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="1"/>
-        <v>5.4097610258252171</v>
+        <v>0.25768871162951451</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="1"/>
-        <v>5.3662439497593954</v>
+        <v>0.2682193264501545</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="1"/>
-        <v>5.2686668012299709</v>
+        <v>0.29285452606145213</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="1"/>
-        <v>5.1684009380699969</v>
+        <v>0.31965835304983242</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
-        <v>5.1068608670238085</v>
+        <v>0.33686494515359761</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="2"/>
-        <v>5.0652268419826996</v>
+        <v>0.34883362110536176</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="2"/>
-        <v>5.0124713843469575</v>
+        <v>0.3643808161491382</v>
       </c>
       <c r="V8" s="3">
         <f t="shared" si="2"/>
-        <v>4.9804242982467652</v>
+        <v>0.37403382755941683</v>
       </c>
       <c r="W8" s="3">
         <f t="shared" si="2"/>
-        <v>4.9154057291602609</v>
+        <v>0.39410371044814696</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="18" x14ac:dyDescent="0.35">
@@ -6239,86 +6268,86 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>2.5000000000000001E-2</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="D9" s="5">
         <v>7</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="1"/>
-        <v>8.0726688801355753</v>
+        <v>1.0546110404714988E-3</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>6.5415202970956496</v>
+        <v>2.5409599380200598E-2</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="1"/>
-        <v>5.8898191672032567</v>
+        <v>6.8378896937559969E-2</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="1"/>
-        <v>5.5225943453085522</v>
+        <v>0.11020326820103764</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
-        <v>5.285236851504278</v>
+        <v>0.14591988388835195</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
-        <v>5.1185966133841054</v>
+        <v>0.17557812030115136</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="1"/>
-        <v>4.9949092190632376</v>
+        <v>0.20020383877718279</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="1"/>
-        <v>4.899340648268236</v>
+        <v>0.22082064184149802</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="1"/>
-        <v>4.8232170846229341</v>
+        <v>0.23826278011715626</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="1"/>
-        <v>4.7611164349968123</v>
+        <v>0.25317583328933924</v>
       </c>
       <c r="O9" s="3">
         <f t="shared" si="1"/>
-        <v>4.7094698576128131</v>
+        <v>0.26605382633690572</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="1"/>
-        <v>4.6658297167259661</v>
+        <v>0.2772760127723547</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="1"/>
-        <v>4.5677873056764389</v>
+        <v>0.30364128323613582</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="1"/>
-        <v>4.466739620214069</v>
+        <v>0.33251132869477368</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>4.4045484957553107</v>
+        <v>0.35114882417944454</v>
       </c>
       <c r="T9" s="3">
         <f t="shared" si="2"/>
-        <v>4.3623930458971678</v>
+        <v>0.3641624557151657</v>
       </c>
       <c r="U9" s="3">
         <f t="shared" si="2"/>
-        <v>4.3088760270388065</v>
+        <v>0.38112937550807674</v>
       </c>
       <c r="V9" s="3">
         <f t="shared" si="2"/>
-        <v>4.2763079364160523</v>
+        <v>0.39170007789428446</v>
       </c>
       <c r="W9" s="3">
         <f t="shared" si="2"/>
-        <v>4.2100867902310712</v>
+        <v>0.41376913430081347</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
@@ -6326,86 +6355,86 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="1"/>
-        <v>7.5708820996917465</v>
+        <v>1.045307581201503E-3</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>6.0594674374634812</v>
+        <v>2.5398101224109477E-2</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="1"/>
-        <v>5.4159623395602381</v>
+        <v>6.877632746011883E-2</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="1"/>
-        <v>5.0526322173635085</v>
+        <v>0.11136377801442864</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="1"/>
-        <v>4.8172755552655318</v>
+        <v>0.14799090490898492</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="1"/>
-        <v>4.6516955373004656</v>
+        <v>0.17858345090364033</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" si="1"/>
-        <v>4.528562147363858</v>
+        <v>0.20410909789534012</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="1"/>
-        <v>4.4332598891823745</v>
+        <v>0.2255676466069825</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="1"/>
-        <v>4.3572330649602122</v>
+        <v>0.24378615321127126</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="1"/>
-        <v>4.2951269601725865</v>
+        <v>0.25941071516962239</v>
       </c>
       <c r="O10" s="3">
         <f t="shared" si="1"/>
-        <v>4.2434127815388507</v>
+        <v>0.27293924471746417</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" si="1"/>
-        <v>4.1996674613167269</v>
+        <v>0.2847561434242476</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" si="1"/>
-        <v>4.1012126677065357</v>
+        <v>0.31262328313426424</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="1"/>
-        <v>3.999452970728302</v>
+        <v>0.34331268627991418</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
-        <v>3.9366590136800532</v>
+        <v>0.36322611995002924</v>
       </c>
       <c r="T10" s="3">
         <f t="shared" si="2"/>
-        <v>3.8940159166292614</v>
+        <v>0.37717968473366287</v>
       </c>
       <c r="U10" s="3">
         <f t="shared" si="2"/>
-        <v>3.8397800938554365</v>
+        <v>0.39543455756409185</v>
       </c>
       <c r="V10" s="3">
         <f t="shared" si="2"/>
-        <v>3.8067161970239343</v>
+        <v>0.40684442823375688</v>
       </c>
       <c r="W10" s="3">
         <f t="shared" si="2"/>
-        <v>3.7393392496715947</v>
+        <v>0.4307595907592261</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
@@ -6413,86 +6442,86 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5">
         <v>9</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="1"/>
-        <v>7.2092832475220154</v>
+        <v>1.0381148228215016E-3</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" si="1"/>
-        <v>5.7147053863830601</v>
+        <v>2.5389163007041152E-2</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="1"/>
-        <v>5.0781186522287127</v>
+        <v>6.9093790331186067E-2</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="1"/>
-        <v>4.7180784581281952</v>
+        <v>0.11230047780266199</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="1"/>
-        <v>4.4844113141850377</v>
+        <v>0.14967697434308722</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
-        <v>4.3197218332928919</v>
+        <v>0.18104768815304631</v>
       </c>
       <c r="K11" s="3">
         <f t="shared" si="1"/>
-        <v>4.1970466369455171</v>
+        <v>0.20733049797574632</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="1"/>
-        <v>4.1019556969397488</v>
+        <v>0.22950344521199756</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="1"/>
-        <v>4.0259941582829777</v>
+        <v>0.24838585469445484</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="1"/>
-        <v>3.9638651576225312</v>
+        <v>0.2646228864447055</v>
       </c>
       <c r="O11" s="3">
         <f t="shared" si="1"/>
-        <v>3.9120744672675589</v>
+        <v>0.27871467179674247</v>
       </c>
       <c r="P11" s="3">
         <f t="shared" si="1"/>
-        <v>3.868220322843273</v>
+        <v>0.29104916350617582</v>
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="1"/>
-        <v>3.7693572792968095</v>
+        <v>0.32023449093195766</v>
       </c>
       <c r="R11" s="3">
         <f t="shared" si="1"/>
-        <v>3.6669055034588203</v>
+        <v>0.35254142525609899</v>
       </c>
       <c r="S11" s="3">
         <f t="shared" si="1"/>
-        <v>3.603526962791074</v>
+        <v>0.3736024736061988</v>
       </c>
       <c r="T11" s="3">
         <f t="shared" si="2"/>
-        <v>3.5604101832335835</v>
+        <v>0.38840832128695701</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" si="2"/>
-        <v>3.5054738998743189</v>
+        <v>0.40784045259136414</v>
       </c>
       <c r="V11" s="3">
         <f t="shared" si="2"/>
-        <v>3.4719249978822151</v>
+        <v>0.42002319676238947</v>
       </c>
       <c r="W11" s="3">
         <f t="shared" si="2"/>
-        <v>3.4034109123013438</v>
+        <v>0.44565476179606434</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="18" x14ac:dyDescent="0.35">
@@ -6501,86 +6530,86 @@
       </c>
       <c r="B12" s="3">
         <f>FINV(B9,B10,B11)</f>
-        <v>4.0721313150582432</v>
+        <v>0.58208046064673946</v>
       </c>
       <c r="D12" s="5">
         <v>10</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="1"/>
-        <v>6.9367281662969829</v>
+        <v>1.0323886717517957E-3</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>5.4563955259127335</v>
+        <v>2.5382015451479729E-2</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="1"/>
-        <v>4.825621493405408</v>
+        <v>6.9353215865514115E-2</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>4.4683415782252816</v>
+        <v>0.11307253037371259</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>4.2360856681886343</v>
+        <v>0.15107670102998205</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>4.0721313150582432</v>
+        <v>0.18310579110520425</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" si="1"/>
-        <v>3.949824068939316</v>
+        <v>0.21003477097292833</v>
       </c>
       <c r="L12" s="3">
         <f t="shared" si="1"/>
-        <v>3.8548908796852293</v>
+        <v>0.23282198856348094</v>
       </c>
       <c r="M12" s="3">
         <f t="shared" si="1"/>
-        <v>3.7789626340915738</v>
+        <v>0.25227901561610766</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="1"/>
-        <v>3.7167918645973668</v>
+        <v>0.26904923289491983</v>
       </c>
       <c r="O12" s="3">
         <f t="shared" si="1"/>
-        <v>3.6649139653923894</v>
+        <v>0.28363389464016858</v>
       </c>
       <c r="P12" s="3">
         <f t="shared" si="1"/>
-        <v>3.620945482936663</v>
+        <v>0.29642339827248271</v>
       </c>
       <c r="Q12" s="3">
         <f t="shared" si="1"/>
-        <v>3.5216732412394327</v>
+        <v>0.32677636392535914</v>
       </c>
       <c r="R12" s="3">
         <f t="shared" si="1"/>
-        <v>3.418543516185037</v>
+        <v>0.36053297767772674</v>
       </c>
       <c r="S12" s="3">
         <f t="shared" si="1"/>
-        <v>3.3545952348799131</v>
+        <v>0.38263360517036188</v>
       </c>
       <c r="T12" s="3">
         <f t="shared" si="2"/>
-        <v>3.3110166678155002</v>
+        <v>0.39821737175484717</v>
       </c>
       <c r="U12" s="3">
         <f t="shared" si="2"/>
-        <v>3.2553960637758714</v>
+        <v>0.41873222270197064</v>
       </c>
       <c r="V12" s="3">
         <f t="shared" si="2"/>
-        <v>3.2213719057027466</v>
+        <v>0.43163092173887024</v>
       </c>
       <c r="W12" s="3">
         <f t="shared" si="2"/>
-        <v>3.151737985034043</v>
+        <v>0.45886706282920098</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -6589,79 +6618,79 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="1"/>
-        <v>6.7241296602391847</v>
+        <v>1.0277226108979778E-3</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>5.2558893119207291</v>
+        <v>2.5376169446047279E-2</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="1"/>
-        <v>4.6300249618293439</v>
+        <v>6.9569186534829339E-2</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="1"/>
-        <v>4.2750715963366144</v>
+        <v>0.11371990313921038</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="1"/>
-        <v>4.0439982220686908</v>
+        <v>0.15225755495079446</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="1"/>
-        <v>3.8806511689100489</v>
+        <v>0.18485104891439419</v>
       </c>
       <c r="K13" s="3">
         <f t="shared" si="1"/>
-        <v>3.7586379183800718</v>
+        <v>0.21233812514661496</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="1"/>
-        <v>3.6638190342878696</v>
+        <v>0.23565937406573856</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" si="1"/>
-        <v>3.5878986691065449</v>
+        <v>0.25561885602307161</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="1"/>
-        <v>3.5256717158880009</v>
+        <v>0.27285770128383735</v>
       </c>
       <c r="O13" s="3">
         <f t="shared" si="1"/>
-        <v>3.4736990510858088</v>
+        <v>0.28787755798459863</v>
       </c>
       <c r="P13" s="3">
         <f t="shared" si="1"/>
-        <v>3.4296130124426694</v>
+        <v>0.30107048777534579</v>
       </c>
       <c r="Q13" s="3">
         <f t="shared" si="1"/>
-        <v>3.3299348224333736</v>
+        <v>0.33246585037266035</v>
       </c>
       <c r="R13" s="3">
         <f t="shared" si="1"/>
-        <v>3.2261447749647711</v>
+        <v>0.3675305941299975</v>
       </c>
       <c r="S13" s="3">
         <f t="shared" si="1"/>
-        <v>3.1616437068797967</v>
+        <v>0.39057862482553835</v>
       </c>
       <c r="T13" s="3">
         <f t="shared" si="2"/>
-        <v>3.1176168087163436</v>
+        <v>0.4068763831582749</v>
       </c>
       <c r="U13" s="3">
         <f t="shared" si="2"/>
-        <v>3.0613302960267763</v>
+        <v>0.42839214220315225</v>
       </c>
       <c r="V13" s="3">
         <f t="shared" si="2"/>
-        <v>3.0268422295052066</v>
+        <v>0.44195727148198583</v>
       </c>
       <c r="W13" s="3">
         <f t="shared" si="2"/>
-        <v>2.956109649570422</v>
+        <v>0.47070023978162595</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
@@ -6676,79 +6705,79 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="1"/>
-        <v>6.5537687530056559</v>
+        <v>1.0238475074617714E-3</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
-        <v>5.0958671657839423</v>
+        <v>2.5371299145639827E-2</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="1"/>
-        <v>4.4741848096377463</v>
+        <v>6.9751776822177439E-2</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="1"/>
-        <v>4.1212086185234424</v>
+        <v>0.11427057932200919</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="1"/>
-        <v>3.8911339339023892</v>
+        <v>0.15326729349436266</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="1"/>
-        <v>3.7282921153925082</v>
+        <v>0.1863500819870175</v>
       </c>
       <c r="K14" s="3">
         <f t="shared" si="1"/>
-        <v>3.6065146422204473</v>
+        <v>0.21432415255430817</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="1"/>
-        <v>3.5117767363148231</v>
+        <v>0.23811409098721109</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="1"/>
-        <v>3.4358456418610581</v>
+        <v>0.25851681562568457</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="1"/>
-        <v>3.3735528498353058</v>
+        <v>0.27617096272572961</v>
       </c>
       <c r="O14" s="3">
         <f t="shared" si="1"/>
-        <v>3.3214813161832897</v>
+        <v>0.29157808661560075</v>
       </c>
       <c r="P14" s="3">
         <f t="shared" si="1"/>
-        <v>3.2772770940334954</v>
+        <v>0.30513135487401039</v>
       </c>
       <c r="Q14" s="3">
         <f t="shared" si="1"/>
-        <v>3.1772011069633002</v>
+        <v>0.33746361824865306</v>
       </c>
       <c r="R14" s="3">
         <f t="shared" si="1"/>
-        <v>3.0727725235527878</v>
+        <v>0.37371573260961438</v>
       </c>
       <c r="S14" s="3">
         <f t="shared" si="1"/>
-        <v>3.0077380459595235</v>
+        <v>0.39763165044040999</v>
       </c>
       <c r="T14" s="3">
         <f t="shared" si="2"/>
-        <v>2.9632779872481714</v>
+        <v>0.41458784819576755</v>
       </c>
       <c r="U14" s="3">
         <f t="shared" si="2"/>
-        <v>2.9063463655921407</v>
+        <v>0.43703295129526504</v>
       </c>
       <c r="V14" s="3">
         <f t="shared" si="2"/>
-        <v>2.8714073631440273</v>
+        <v>0.4512209490805299</v>
       </c>
       <c r="W14" s="3">
         <f t="shared" si="2"/>
-        <v>2.7996011318380258</v>
+        <v>0.48138433932847247</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
@@ -6763,79 +6792,79 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="1"/>
-        <v>6.414254300250585</v>
+        <v>1.0205781439902536E-3</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="1"/>
-        <v>4.9652657229043431</v>
+        <v>2.5367179095273123E-2</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="1"/>
-        <v>4.3471780827098545</v>
+        <v>6.9908170347764656E-2</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="1"/>
-        <v>3.9958975534941668</v>
+        <v>0.11474474165613598</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="1"/>
-        <v>3.7666740552333313</v>
+        <v>0.15414068818165846</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="1"/>
-        <v>3.6042563940468262</v>
+        <v>0.18765177335702413</v>
       </c>
       <c r="K15" s="3">
         <f t="shared" si="1"/>
-        <v>3.4826693293426567</v>
+        <v>0.21605458453625534</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="1"/>
-        <v>3.387987325389608</v>
+        <v>0.24025926394404698</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="1"/>
-        <v>3.3120324100531073</v>
+        <v>0.26105601062718881</v>
       </c>
       <c r="N15" s="3">
         <f t="shared" si="1"/>
-        <v>3.249667950133122</v>
+        <v>0.27908086463149345</v>
       </c>
       <c r="O15" s="3">
         <f t="shared" si="1"/>
-        <v>3.1974961857124629</v>
+        <v>0.29483496039746704</v>
       </c>
       <c r="P15" s="3">
         <f t="shared" si="1"/>
-        <v>3.153175177661617</v>
+        <v>0.30871216755366587</v>
       </c>
       <c r="Q15" s="3">
         <f t="shared" si="1"/>
-        <v>3.0527132473829535</v>
+        <v>0.34189151377854726</v>
       </c>
       <c r="R15" s="3">
         <f t="shared" si="1"/>
-        <v>2.9476708466886934</v>
+        <v>0.37922695623529262</v>
       </c>
       <c r="S15" s="3">
         <f t="shared" si="1"/>
-        <v>2.8821239542175419</v>
+        <v>0.40394152536748557</v>
       </c>
       <c r="T15" s="3">
         <f t="shared" si="2"/>
-        <v>2.8372470346007477</v>
+        <v>0.42150744818288316</v>
       </c>
       <c r="U15" s="3">
         <f t="shared" si="2"/>
-        <v>2.7796926930304515</v>
+        <v>0.44481873022184498</v>
       </c>
       <c r="V15" s="3">
         <f t="shared" si="2"/>
-        <v>2.7443168337059447</v>
+        <v>0.45959093219915487</v>
       </c>
       <c r="W15" s="3">
         <f t="shared" si="2"/>
-        <v>2.6714646650186227</v>
+        <v>0.49109765354082979</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="18" x14ac:dyDescent="0.35">
@@ -6850,79 +6879,79 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="1"/>
-        <v>6.2979386311029479</v>
+        <v>1.017782901075154E-3</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
-        <v>4.8566978606751672</v>
+        <v>2.5363648333288129E-2</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="1"/>
-        <v>4.241727630359188</v>
+        <v>7.0043627417395379E-2</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="1"/>
-        <v>3.8919144377657129</v>
+        <v>0.11515731604290867</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="1"/>
-        <v>3.6634231139830886</v>
+        <v>0.15490366697779517</v>
       </c>
       <c r="J16" s="3">
         <f t="shared" si="1"/>
-        <v>3.5013649360015529</v>
+        <v>0.18879282389315222</v>
       </c>
       <c r="K16" s="3">
         <f t="shared" si="1"/>
-        <v>3.3799328776529314</v>
+        <v>0.21757603445831125</v>
       </c>
       <c r="L16" s="3">
         <f t="shared" si="1"/>
-        <v>3.2852880186245335</v>
+        <v>0.2421503768162841</v>
       </c>
       <c r="M16" s="3">
         <f t="shared" si="1"/>
-        <v>3.2093003408966867</v>
+        <v>0.26329976603315275</v>
       </c>
       <c r="N16" s="3">
         <f t="shared" si="1"/>
-        <v>3.1468611935575752</v>
+        <v>0.28165763158122764</v>
       </c>
       <c r="O16" s="3">
         <f t="shared" si="1"/>
-        <v>3.0945897908988029</v>
+        <v>0.29772447186265522</v>
       </c>
       <c r="P16" s="3">
         <f t="shared" si="1"/>
-        <v>3.0501547888185927</v>
+        <v>0.31189456389560855</v>
       </c>
       <c r="Q16" s="3">
         <f t="shared" si="1"/>
-        <v>2.9493211334022709</v>
+        <v>0.34584381118510593</v>
       </c>
       <c r="R16" s="3">
         <f t="shared" si="1"/>
-        <v>2.8436912227546562</v>
+        <v>0.38417217618056931</v>
       </c>
       <c r="S16" s="3">
         <f t="shared" si="1"/>
-        <v>2.7776536722027463</v>
+        <v>0.40962462896456048</v>
       </c>
       <c r="T16" s="3">
         <f t="shared" si="2"/>
-        <v>2.7323767131231644</v>
+        <v>0.4277572269216981</v>
       </c>
       <c r="U16" s="3">
         <f t="shared" si="2"/>
-        <v>2.6742228161525508</v>
+        <v>0.45187850911228705</v>
       </c>
       <c r="V16" s="3">
         <f t="shared" si="2"/>
-        <v>2.6384247638739122</v>
+        <v>0.46720033486626361</v>
       </c>
       <c r="W16" s="3">
         <f t="shared" si="2"/>
-        <v>2.5645559563780078</v>
+        <v>0.49998106578999013</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="18" x14ac:dyDescent="0.35">
@@ -6941,79 +6970,79 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="1"/>
-        <v>6.1995009378011057</v>
+        <v>1.0153656901709402E-3</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>4.7650482838882056</v>
+        <v>2.5360588869408552E-2</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="1"/>
-        <v>4.1528040300628728</v>
+        <v>7.0162088333175346E-2</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="1"/>
-        <v>3.8042713418410128</v>
+        <v>0.11551957991003842</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="1"/>
-        <v>3.5764153492790598</v>
+        <v>0.15557596307848712</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="1"/>
-        <v>3.414664657735774</v>
+        <v>0.18980133641522939</v>
       </c>
       <c r="K17" s="3">
         <f t="shared" si="1"/>
-        <v>3.2933598137323106</v>
+        <v>0.21892437915340082</v>
       </c>
       <c r="L17" s="3">
         <f t="shared" si="1"/>
-        <v>3.1987380785407584</v>
+        <v>0.24383032069371238</v>
       </c>
       <c r="M17" s="3">
         <f t="shared" si="1"/>
-        <v>3.1227117263033253</v>
+        <v>0.26529721804099055</v>
       </c>
       <c r="N17" s="3">
         <f t="shared" si="1"/>
-        <v>3.0601968514112481</v>
+        <v>0.2839559298942953</v>
       </c>
       <c r="O17" s="3">
         <f t="shared" si="1"/>
-        <v>3.0078277178817077</v>
+        <v>0.30030617814592614</v>
       </c>
       <c r="P17" s="3">
         <f t="shared" si="1"/>
-        <v>2.9632823982322472</v>
+        <v>0.31474243094286769</v>
       </c>
       <c r="Q17" s="3">
         <f t="shared" si="1"/>
-        <v>2.8620925304635034</v>
+        <v>0.34939471360768853</v>
       </c>
       <c r="R17" s="3">
         <f t="shared" si="1"/>
-        <v>2.7559019509779965</v>
+        <v>0.38863685813810162</v>
       </c>
       <c r="S17" s="3">
         <f t="shared" si="1"/>
-        <v>2.6893955969185441</v>
+        <v>0.4147734877909437</v>
       </c>
       <c r="T17" s="3">
         <f t="shared" si="2"/>
-        <v>2.6437354709333936</v>
+        <v>0.43343446107446043</v>
       </c>
       <c r="U17" s="3">
         <f t="shared" si="2"/>
-        <v>2.5850053267419866</v>
+        <v>0.45831544893416287</v>
       </c>
       <c r="V17" s="3">
         <f t="shared" si="2"/>
-        <v>2.5487999238457277</v>
+        <v>0.47415576751959615</v>
       </c>
       <c r="W17" s="3">
         <f t="shared" si="2"/>
-        <v>2.4739444812463796</v>
+        <v>0.5081477538617315</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
@@ -7022,79 +7051,79 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="1"/>
-        <v>6.115127197700355</v>
+        <v>1.0132547290558785E-3</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
-        <v>4.6866654010979474</v>
+        <v>2.5357912242029837E-2</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="1"/>
-        <v>4.0768230619624797</v>
+        <v>7.0266563004208207E-2</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="1"/>
-        <v>3.7294165455930486</v>
+        <v>0.11584021365251683</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="1"/>
-        <v>3.5021163355058786</v>
+        <v>0.15617286386272558</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="1"/>
-        <v>3.3406309395469478</v>
+        <v>0.19069920128289661</v>
       </c>
       <c r="K18" s="3">
         <f t="shared" si="1"/>
-        <v>3.2194313183202969</v>
+        <v>0.22012769417516706</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="1"/>
-        <v>3.1248222143022684</v>
+        <v>0.24533279354239851</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="1"/>
-        <v>3.0487534580366811</v>
+        <v>0.26708710350232417</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="1"/>
-        <v>2.9861631744340622</v>
+        <v>0.28601898445338703</v>
       </c>
       <c r="O18" s="3">
         <f t="shared" si="1"/>
-        <v>2.9336990597818038</v>
+        <v>0.302627293885393</v>
       </c>
       <c r="P18" s="3">
         <f t="shared" si="1"/>
-        <v>2.889047611448845</v>
+        <v>0.31730653181130186</v>
       </c>
       <c r="Q18" s="3">
         <f t="shared" si="1"/>
-        <v>2.7875175724345596</v>
+        <v>0.35260350125343071</v>
       </c>
       <c r="R18" s="3">
         <f t="shared" si="1"/>
-        <v>2.680792960812151</v>
+        <v>0.39268968399799842</v>
       </c>
       <c r="S18" s="3">
         <f t="shared" si="1"/>
-        <v>2.6138392946926139</v>
+        <v>0.41946273319457711</v>
       </c>
       <c r="T18" s="3">
         <f t="shared" si="2"/>
-        <v>2.5678125980198572</v>
+        <v>0.4386178074086779</v>
       </c>
       <c r="U18" s="3">
         <f t="shared" si="2"/>
-        <v>2.5085292151857979</v>
+        <v>0.46421321581841735</v>
       </c>
       <c r="V18" s="3">
         <f t="shared" si="2"/>
-        <v>2.4719311941956184</v>
+        <v>0.48054384202982081</v>
       </c>
       <c r="W18" s="3">
         <f t="shared" si="2"/>
-        <v>2.3961191928000098</v>
+        <v>0.51568994459680872</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
@@ -7103,79 +7132,79 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="1"/>
-        <v>6.0420133439571213</v>
+        <v>1.0113953174186179E-3</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>4.6188743275143969</v>
+        <v>2.5355550824699653E-2</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="1"/>
-        <v>4.0111631180738794</v>
+        <v>7.0359390249534207E-2</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="1"/>
-        <v>3.6647540910362095</v>
+        <v>0.11612600802188805</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="1"/>
-        <v>3.4379437009100964</v>
+        <v>0.15670639807821604</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="1"/>
-        <v>3.2766890403083679</v>
+        <v>0.19150372749282718</v>
       </c>
       <c r="K19" s="3">
         <f t="shared" si="1"/>
-        <v>3.1555770906793592</v>
+        <v>0.22120827261758524</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="1"/>
-        <v>3.0609727563989764</v>
+        <v>0.24668464983669469</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="1"/>
-        <v>2.9848594289141062</v>
+        <v>0.26870038952790298</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="1"/>
-        <v>2.922194967244919</v>
+        <v>0.28788144509214664</v>
       </c>
       <c r="O19" s="3">
         <f t="shared" si="1"/>
-        <v>2.8696391288021106</v>
+        <v>0.30472575848219663</v>
       </c>
       <c r="P19" s="3">
         <f t="shared" si="1"/>
-        <v>2.8248859937650623</v>
+        <v>0.31962774420929446</v>
       </c>
       <c r="Q19" s="3">
         <f t="shared" si="1"/>
-        <v>2.7230318334422634</v>
+        <v>0.35551815365775946</v>
       </c>
       <c r="R19" s="3">
         <f t="shared" si="1"/>
-        <v>2.6157991389296891</v>
+        <v>0.39638655568149128</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="1"/>
-        <v>2.5484189910544557</v>
+        <v>0.42375332613686612</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" si="2"/>
-        <v>2.5020418305663599</v>
+        <v>0.44337166945853895</v>
       </c>
       <c r="U19" s="3">
         <f t="shared" si="2"/>
-        <v>2.4422276254829769</v>
+        <v>0.46964051747449959</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" si="2"/>
-        <v>2.4052514155158007</v>
+        <v>0.48643580566443068</v>
       </c>
       <c r="W19" s="3">
         <f t="shared" si="2"/>
-        <v>2.3285125698615841</v>
+        <v>0.52268373362742049</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
@@ -7184,79 +7213,79 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="1"/>
-        <v>5.9780524647896147</v>
+        <v>1.0097450434081623E-3</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
-        <v>4.5596717126520039</v>
+        <v>2.535345203315242E-2</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="1"/>
-        <v>3.9538633649489681</v>
+        <v>7.0442414956330149E-2</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="1"/>
-        <v>3.6083435718954346</v>
+        <v>0.11638235209878585</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" ref="F20:U31" si="3">FINV($B$9,I$2,$D20)</f>
-        <v>3.3819678058752425</v>
+        <v>0.15718616136624453</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="3"/>
-        <v>3.2209153074898556</v>
+        <v>0.19222878435541521</v>
       </c>
       <c r="K20" s="3">
         <f t="shared" si="3"/>
-        <v>3.099876901694242</v>
+        <v>0.22218404584393153</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="3"/>
-        <v>3.0052714456775065</v>
+        <v>0.24790756153537316</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="3"/>
-        <v>2.9291124931232653</v>
+        <v>0.27016213936232097</v>
       </c>
       <c r="N20" s="3">
         <f t="shared" si="3"/>
-        <v>2.8663756788330872</v>
+        <v>0.28957142690414611</v>
       </c>
       <c r="O20" s="3">
         <f t="shared" si="3"/>
-        <v>2.8137316494987781</v>
+        <v>0.30663242522222162</v>
       </c>
       <c r="P20" s="3">
         <f t="shared" si="3"/>
-        <v>2.7688813472407565</v>
+        <v>0.32173937704288891</v>
       </c>
       <c r="Q20" s="3">
         <f t="shared" si="3"/>
-        <v>2.6667187865226274</v>
+        <v>0.35817795395711982</v>
       </c>
       <c r="R20" s="3">
         <f t="shared" si="3"/>
-        <v>2.5590029738426763</v>
+        <v>0.39977348803864621</v>
       </c>
       <c r="S20" s="3">
         <f t="shared" si="3"/>
-        <v>2.4912163338358373</v>
+        <v>0.42769561817605506</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" si="2"/>
-        <v>2.444504197490085</v>
+        <v>0.44774936658571696</v>
       </c>
       <c r="U20" s="3">
         <f t="shared" si="2"/>
-        <v>2.384180812111337</v>
+        <v>0.47465440160180766</v>
       </c>
       <c r="V20" s="3">
         <f t="shared" si="2"/>
-        <v>2.3468404149136539</v>
+        <v>0.49189091373482979</v>
       </c>
       <c r="W20" s="3">
         <f t="shared" si="2"/>
-        <v>2.2692037900772948</v>
+        <v>0.52919259901544613</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
@@ -7265,79 +7294,79 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="1"/>
-        <v>5.9216312623366552</v>
+        <v>1.0082705178719876E-3</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="3"/>
-        <v>4.5075279951686804</v>
+        <v>2.5351574363325032E-2</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="3"/>
-        <v>3.9034284918229427</v>
+        <v>7.0517111931328647E-2</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="3"/>
-        <v>3.5587060985855814</v>
+        <v>0.11661357739263609</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="3"/>
-        <v>3.3327183728047252</v>
+        <v>0.15761990261341266</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="3"/>
-        <v>3.1718442039434258</v>
+        <v>0.19288561726771414</v>
       </c>
       <c r="K21" s="3">
         <f t="shared" si="3"/>
-        <v>3.0508678753984744</v>
+        <v>0.22306960371284487</v>
       </c>
       <c r="L21" s="3">
         <f t="shared" si="3"/>
-        <v>2.9562568887350005</v>
+        <v>0.24901921579698783</v>
       </c>
       <c r="M21" s="3">
         <f t="shared" si="3"/>
-        <v>2.8800520467237973</v>
+        <v>0.27149286256295019</v>
       </c>
       <c r="N21" s="3">
         <f t="shared" si="3"/>
-        <v>2.8172450772583764</v>
+        <v>0.29111199102204494</v>
       </c>
       <c r="O21" s="3">
         <f t="shared" si="3"/>
-        <v>2.764516507194636</v>
+        <v>0.30837265406742864</v>
       </c>
       <c r="P21" s="3">
         <f t="shared" si="3"/>
-        <v>2.7195735186943755</v>
+        <v>0.32366885960524522</v>
       </c>
       <c r="Q21" s="3">
         <f t="shared" si="3"/>
-        <v>2.6171177393947795</v>
+        <v>0.36061539709839707</v>
       </c>
       <c r="R21" s="3">
         <f t="shared" si="3"/>
-        <v>2.5089426210844068</v>
+        <v>0.40288873879731951</v>
       </c>
       <c r="S21" s="3">
         <f t="shared" si="3"/>
-        <v>2.4407685407380906</v>
+        <v>0.43133161131072734</v>
       </c>
       <c r="T21" s="3">
         <f t="shared" si="2"/>
-        <v>2.3937362262840964</v>
+        <v>0.45179547752791888</v>
       </c>
       <c r="U21" s="3">
         <f t="shared" si="3"/>
-        <v>2.3329244234594579</v>
+        <v>0.47930269965860811</v>
       </c>
       <c r="V21" s="3">
         <f t="shared" si="2"/>
-        <v>2.2952333387745694</v>
+        <v>0.4969589308260321</v>
       </c>
       <c r="W21" s="3">
         <f t="shared" si="2"/>
-        <v>2.2167271674975608</v>
+        <v>0.53527001133536534</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
@@ -7346,79 +7375,79 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="1"/>
-        <v>5.8714937658080757</v>
+        <v>1.0069450971157963E-3</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="3"/>
-        <v>4.4612554959192474</v>
+        <v>2.5349884618969969E-2</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="3"/>
-        <v>3.8586986662732152</v>
+        <v>7.0584674265413178E-2</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="3"/>
-        <v>3.5146951622584099</v>
+        <v>0.11682320526524601</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="3"/>
-        <v>3.2890558456804069</v>
+        <v>0.15801394834141053</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="3"/>
-        <v>3.128339961897094</v>
+        <v>0.19348344139365939</v>
       </c>
       <c r="K22" s="3">
         <f t="shared" si="3"/>
-        <v>3.0074163305213055</v>
+        <v>0.22387694045888326</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="3"/>
-        <v>2.9127965262101236</v>
+        <v>0.25003419400576166</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="3"/>
-        <v>2.8365460861048133</v>
+        <v>0.27270950916426584</v>
       </c>
       <c r="N22" s="3">
         <f t="shared" si="3"/>
-        <v>2.7736713751990809</v>
+        <v>0.29252223798395915</v>
       </c>
       <c r="O22" s="3">
         <f t="shared" si="3"/>
-        <v>2.720861925432783</v>
+        <v>0.30996749053548606</v>
       </c>
       <c r="P22" s="3">
         <f t="shared" si="3"/>
-        <v>2.67583061868205</v>
+        <v>0.32543899437234769</v>
       </c>
       <c r="Q22" s="3">
         <f t="shared" si="3"/>
-        <v>2.5730961411916615</v>
+        <v>0.36285761169591924</v>
       </c>
       <c r="R22" s="3">
         <f t="shared" si="3"/>
-        <v>2.4644842975421208</v>
+        <v>0.40576440312373652</v>
       </c>
       <c r="S22" s="3">
         <f t="shared" si="3"/>
-        <v>2.3959408493940648</v>
+        <v>0.43469665433218513</v>
       </c>
       <c r="T22" s="3">
         <f t="shared" si="2"/>
-        <v>2.3486024327417465</v>
+        <v>0.45554760251285092</v>
       </c>
       <c r="U22" s="3">
         <f t="shared" si="2"/>
-        <v>2.2873220448574307</v>
+        <v>0.48362586777175431</v>
       </c>
       <c r="V22" s="3">
         <f t="shared" si="2"/>
-        <v>2.2492932300230404</v>
+        <v>0.50168201685224512</v>
       </c>
       <c r="W22" s="3">
         <f t="shared" si="2"/>
-        <v>2.1699448034087188</v>
+        <v>0.54096140505069557</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
@@ -7427,79 +7456,79 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="1"/>
-        <v>5.8266477641598238</v>
+        <v>1.005747261981244E-3</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="3"/>
-        <v>4.4199181664208549</v>
+        <v>2.5348355932014947E-2</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="3"/>
-        <v>3.8187606805913683</v>
+        <v>7.0646077533450619E-2</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="3"/>
-        <v>3.4754084620526484</v>
+        <v>0.11701412796418653</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="3"/>
-        <v>3.2500835876780974</v>
+        <v>0.15837351508560404</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="3"/>
-        <v>3.0895089993607208</v>
+        <v>0.19402988085257528</v>
       </c>
       <c r="K23" s="3">
         <f t="shared" si="3"/>
-        <v>2.9686303350106864</v>
+        <v>0.2246160088161063</v>
       </c>
       <c r="L23" s="3">
         <f t="shared" si="3"/>
-        <v>2.8739992795564135</v>
+        <v>0.25096462715786988</v>
       </c>
       <c r="M23" s="3">
         <f t="shared" si="3"/>
-        <v>2.7977039195030247</v>
+        <v>0.27382621317923295</v>
       </c>
       <c r="N23" s="3">
         <f t="shared" si="3"/>
-        <v>2.7347639889588025</v>
+        <v>0.29381812756953213</v>
       </c>
       <c r="O23" s="3">
         <f t="shared" si="3"/>
-        <v>2.6818772612080983</v>
+        <v>0.31143455165246714</v>
       </c>
       <c r="P23" s="3">
         <f t="shared" si="3"/>
-        <v>2.6367618453327721</v>
+        <v>0.32706890034510183</v>
       </c>
       <c r="Q23" s="3">
         <f t="shared" si="3"/>
-        <v>2.5337624655786355</v>
+        <v>0.36492743548288542</v>
       </c>
       <c r="R23" s="3">
         <f t="shared" si="3"/>
-        <v>2.4247352225884962</v>
+        <v>0.40842762523266013</v>
       </c>
       <c r="S23" s="3">
         <f t="shared" si="3"/>
-        <v>2.3558394953430204</v>
+        <v>0.4378207351955013</v>
       </c>
       <c r="T23" s="3">
         <f t="shared" si="2"/>
-        <v>2.3082083253639287</v>
+        <v>0.45903770795075716</v>
       </c>
       <c r="U23" s="3">
         <f t="shared" si="2"/>
-        <v>2.2464782389551528</v>
+        <v>0.48765839418868911</v>
       </c>
       <c r="V23" s="3">
         <f t="shared" si="2"/>
-        <v>2.2081240919047431</v>
+        <v>0.50609617045222577</v>
       </c>
       <c r="W23" s="3">
         <f t="shared" si="2"/>
-        <v>2.1279597011766107</v>
+        <v>0.5463056896898929</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
@@ -7508,79 +7537,79 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="1"/>
-        <v>5.7862991330089324</v>
+        <v>1.0046594427438199E-3</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" si="3"/>
-        <v>4.3827684394668065</v>
+        <v>2.5346966323238577E-2</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="3"/>
-        <v>3.7828858591420609</v>
+        <v>7.0702127202971463E-2</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="3"/>
-        <v>3.4401263263410256</v>
+        <v>0.11718874316849713</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="3"/>
-        <v>3.2150865809890168</v>
+        <v>0.15870294283319211</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="3"/>
-        <v>3.0546387834300619</v>
+        <v>0.19453129844413203</v>
       </c>
       <c r="K24" s="3">
         <f t="shared" si="3"/>
-        <v>2.9337986715102757</v>
+        <v>0.22529513766764042</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="3"/>
-        <v>2.8391545838698651</v>
+        <v>0.25182069148926495</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="3"/>
-        <v>2.7628152463682563</v>
+        <v>0.27485485647734254</v>
       </c>
       <c r="N24" s="3">
         <f t="shared" si="3"/>
-        <v>2.6998126513896539</v>
+        <v>0.29501310210808379</v>
       </c>
       <c r="O24" s="3">
         <f t="shared" si="3"/>
-        <v>2.646852143047473</v>
+        <v>0.31278870096946459</v>
       </c>
       <c r="P24" s="3">
         <f t="shared" si="3"/>
-        <v>2.6016566419647695</v>
+        <v>0.32857473312837288</v>
       </c>
       <c r="Q24" s="3">
         <f t="shared" si="3"/>
-        <v>2.4984054078245297</v>
+        <v>0.36684423977009734</v>
       </c>
       <c r="R24" s="3">
         <f t="shared" si="3"/>
-        <v>2.3889828526690984</v>
+        <v>0.41090153136930307</v>
       </c>
       <c r="S24" s="3">
         <f t="shared" si="3"/>
-        <v>2.3197509703553534</v>
+        <v>0.44072947878662433</v>
       </c>
       <c r="T24" s="3">
         <f t="shared" si="2"/>
-        <v>2.2718396808943955</v>
+        <v>0.46229316630090617</v>
       </c>
       <c r="U24" s="3">
         <f t="shared" si="2"/>
-        <v>2.2096778450768975</v>
+        <v>0.49142988971158003</v>
       </c>
       <c r="V24" s="3">
         <f t="shared" si="2"/>
-        <v>2.1710102031132674</v>
+        <v>0.51023234838058573</v>
       </c>
       <c r="W24" s="3">
         <f t="shared" si="2"/>
-        <v>2.0900551164737893</v>
+        <v>0.55133642373523384</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
@@ -7589,79 +7618,79 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="1"/>
-        <v>5.7498048257043335</v>
+        <v>1.003667153087658E-3</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="3"/>
-        <v>4.3492021547074273</v>
+        <v>2.5345697638697044E-2</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="3"/>
-        <v>3.7504857895219375</v>
+        <v>7.075349416128851E-2</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="3"/>
-        <v>3.4082678349520577</v>
+        <v>0.11734905540779517</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="3"/>
-        <v>3.1834877602357818</v>
+        <v>0.15900587187459692</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="3"/>
-        <v>3.0231542867700085</v>
+        <v>0.19499304651695326</v>
       </c>
       <c r="K25" s="3">
         <f t="shared" si="3"/>
-        <v>2.9023473699323405</v>
+        <v>0.225921350972212</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="3"/>
-        <v>2.8076889698993881</v>
+        <v>0.25261098813308253</v>
       </c>
       <c r="M25" s="3">
         <f t="shared" si="3"/>
-        <v>2.7313067729359077</v>
+        <v>0.27580550188716413</v>
       </c>
       <c r="N25" s="3">
         <f t="shared" si="3"/>
-        <v>2.668244051184669</v>
+        <v>0.29611856634520467</v>
       </c>
       <c r="O25" s="3">
         <f t="shared" si="3"/>
-        <v>2.6152131277083006</v>
+        <v>0.31404256929219321</v>
       </c>
       <c r="P25" s="3">
         <f t="shared" si="3"/>
-        <v>2.5699413670146583</v>
+        <v>0.32997024140715114</v>
       </c>
       <c r="Q25" s="3">
         <f t="shared" si="3"/>
-        <v>2.4664505805223915</v>
+        <v>0.36862456922081277</v>
       </c>
       <c r="R25" s="3">
         <f t="shared" si="3"/>
-        <v>2.356651600514887</v>
+        <v>0.41320595693472478</v>
       </c>
       <c r="S25" s="3">
         <f t="shared" si="3"/>
-        <v>2.2870987563952054</v>
+        <v>0.44344492653432699</v>
       </c>
       <c r="T25" s="3">
         <f t="shared" si="2"/>
-        <v>2.2389192891347984</v>
+        <v>0.46533756990142316</v>
       </c>
       <c r="U25" s="3">
         <f t="shared" si="2"/>
-        <v>2.176342739418279</v>
+        <v>0.49496594269561933</v>
       </c>
       <c r="V25" s="3">
         <f t="shared" si="2"/>
-        <v>2.1373728884239154</v>
+        <v>0.51411734408405318</v>
       </c>
       <c r="W25" s="3">
         <f t="shared" si="2"/>
-        <v>2.0556513517729997</v>
+        <v>0.55608273749357817</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -7670,79 +7699,79 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="1"/>
-        <v>5.7166386275180701</v>
+        <v>1.002758342323274E-3</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="3"/>
-        <v>4.3187258074524504</v>
+        <v>2.5344534752231179E-2</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="3"/>
-        <v>3.7210801909151101</v>
+        <v>7.0800741695811506E-2</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="3"/>
-        <v>3.3793589877391219</v>
+        <v>0.11749675349863115</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="3"/>
-        <v>3.154816342533115</v>
+        <v>0.15928537846289567</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="3"/>
-        <v>2.9945864110906029</v>
+        <v>0.19541966016986131</v>
       </c>
       <c r="K26" s="3">
         <f t="shared" si="3"/>
-        <v>2.8738081880378892</v>
+        <v>0.2265006142148844</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="3"/>
-        <v>2.779134581153115</v>
+        <v>0.25334283736012414</v>
       </c>
       <c r="M26" s="3">
         <f t="shared" si="3"/>
-        <v>2.7027107536423749</v>
+        <v>0.27668672970897912</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="3"/>
-        <v>2.6395903910728991</v>
+        <v>0.29714426111227232</v>
       </c>
       <c r="O26" s="3">
         <f t="shared" si="3"/>
-        <v>2.5864922703654218</v>
+        <v>0.31520696095098527</v>
       </c>
       <c r="P26" s="3">
         <f t="shared" si="3"/>
-        <v>2.5411478730881343</v>
+        <v>0.33126720183868463</v>
       </c>
       <c r="Q26" s="3">
         <f t="shared" si="3"/>
-        <v>2.4374291090774944</v>
+        <v>0.37028264382570725</v>
       </c>
       <c r="R26" s="3">
         <f t="shared" si="3"/>
-        <v>2.3272714446086176</v>
+        <v>0.41535801939856631</v>
       </c>
       <c r="S26" s="3">
         <f t="shared" si="3"/>
-        <v>2.2574119437273965</v>
+        <v>0.44598615222740129</v>
       </c>
       <c r="T26" s="3">
         <f t="shared" si="2"/>
-        <v>2.2089755775532125</v>
+        <v>0.46819137485255541</v>
       </c>
       <c r="U26" s="3">
         <f t="shared" si="2"/>
-        <v>2.1460004692133543</v>
+        <v>0.49828879676305782</v>
       </c>
       <c r="V26" s="3">
         <f t="shared" si="2"/>
-        <v>2.1067391595840572</v>
+        <v>0.51777448479845967</v>
       </c>
       <c r="W26" s="3">
         <f t="shared" si="2"/>
-        <v>2.0242744132026882</v>
+        <v>0.56057006654926655</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
@@ -7751,79 +7780,79 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="1"/>
-        <v>5.6863658097817762</v>
+        <v>1.0019229042860349E-3</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="3"/>
-        <v>4.2909323669963095</v>
+        <v>2.5343464959500881E-2</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="3"/>
-        <v>3.6942732131431537</v>
+        <v>7.0844346233886107E-2</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="3"/>
-        <v>3.3530092361482979</v>
+        <v>0.11763327036586986</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="3"/>
-        <v>3.1286844836294962</v>
+        <v>0.1595440800649551</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" si="3"/>
-        <v>2.9685487148092489</v>
+        <v>0.19581500770017701</v>
       </c>
       <c r="K27" s="3">
         <f t="shared" si="3"/>
-        <v>2.8477953823048523</v>
+        <v>0.22703802693141117</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="3"/>
-        <v>2.7531059719426976</v>
+        <v>0.25402250906795815</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="3"/>
-        <v>2.6766418068582309</v>
+        <v>0.27750590194709157</v>
       </c>
       <c r="N27" s="3">
         <f t="shared" si="3"/>
-        <v>2.6134662154275885</v>
+        <v>0.29809855734675456</v>
       </c>
       <c r="O27" s="3">
         <f t="shared" si="3"/>
-        <v>2.5603039604296716</v>
+        <v>0.31629117405733659</v>
       </c>
       <c r="P27" s="3">
         <f t="shared" si="3"/>
-        <v>2.5148903486239531</v>
+        <v>0.33247576242331339</v>
       </c>
       <c r="Q27" s="3">
         <f t="shared" si="3"/>
-        <v>2.4109544834360928</v>
+        <v>0.37183075674912969</v>
       </c>
       <c r="R27" s="3">
         <f t="shared" si="3"/>
-        <v>2.30045478849217</v>
+        <v>0.41737257422398427</v>
       </c>
       <c r="S27" s="3">
         <f t="shared" si="3"/>
-        <v>2.2303020947471461</v>
+        <v>0.44836975329719719</v>
       </c>
       <c r="T27" s="3">
         <f t="shared" si="2"/>
-        <v>2.1816194786595009</v>
+        <v>0.47087241551006881</v>
       </c>
       <c r="U27" s="3">
         <f t="shared" si="2"/>
-        <v>2.1182611256701547</v>
+        <v>0.50141789333371667</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" si="2"/>
-        <v>2.0787185923955493</v>
+        <v>0.52122419015269794</v>
       </c>
       <c r="W27" s="3">
         <f t="shared" si="2"/>
-        <v>1.9955328980568232</v>
+        <v>0.56482074047498354</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
@@ -7832,79 +7861,79 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="1"/>
-        <v>5.5675349965107754</v>
+        <v>9.9858758963669797E-4</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="3"/>
-        <v>4.182060590996115</v>
+        <v>2.5339186390510762E-2</v>
       </c>
       <c r="G28" s="3">
         <f t="shared" si="3"/>
-        <v>3.5893591203518564</v>
+        <v>7.1020087356894815E-2</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="3"/>
-        <v>3.2499253785634048</v>
+        <v>0.11818551182274412</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="3"/>
-        <v>3.0264664092158839</v>
+        <v>0.16059409788705351</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="3"/>
-        <v>2.8666961539752491</v>
+        <v>0.19742452434935115</v>
       </c>
       <c r="K28" s="3">
         <f t="shared" si="3"/>
-        <v>2.7460271763494557</v>
+        <v>0.22923198104317979</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="3"/>
-        <v>2.6512562592180129</v>
+        <v>0.25680429186987519</v>
       </c>
       <c r="M28" s="3">
         <f t="shared" si="3"/>
-        <v>2.5746101337030778</v>
+        <v>0.28086651496199089</v>
       </c>
       <c r="N28" s="3">
         <f t="shared" si="3"/>
-        <v>2.5111913013569533</v>
+        <v>0.30202203743654576</v>
       </c>
       <c r="O28" s="3">
         <f t="shared" si="3"/>
-        <v>2.4577489414297116</v>
+        <v>0.3207578292509089</v>
       </c>
       <c r="P28" s="3">
         <f t="shared" si="3"/>
-        <v>2.4120340341663908</v>
+        <v>0.33746412057973779</v>
       </c>
       <c r="Q28" s="3">
         <f t="shared" si="3"/>
-        <v>2.3071538832446663</v>
+        <v>0.3782526697525232</v>
       </c>
       <c r="R28" s="3">
         <f t="shared" si="3"/>
-        <v>2.1951602741050329</v>
+        <v>0.42578513334528278</v>
       </c>
       <c r="S28" s="3">
         <f t="shared" si="3"/>
-        <v>2.1237175231782426</v>
+        <v>0.45837507859732346</v>
       </c>
       <c r="T28" s="3">
         <f t="shared" si="2"/>
-        <v>2.0739437504716296</v>
+        <v>0.48217315429726232</v>
       </c>
       <c r="U28" s="3">
         <f t="shared" si="2"/>
-        <v>2.0088723859350663</v>
+        <v>0.51469029034574532</v>
       </c>
       <c r="V28" s="3">
         <f t="shared" si="2"/>
-        <v>1.9680608340696524</v>
+        <v>0.53592285016177776</v>
       </c>
       <c r="W28" s="3">
         <f t="shared" si="2"/>
-        <v>1.8815726011497234</v>
+        <v>0.58314176387982541</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
@@ -7913,79 +7942,79 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="1"/>
-        <v>5.423937151592205</v>
+        <v>9.9443306706569249E-4</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="3"/>
-        <v>4.0509920759367004</v>
+        <v>2.5333839533332458E-2</v>
       </c>
       <c r="G29" s="3">
         <f t="shared" si="3"/>
-        <v>3.4632596595348422</v>
+        <v>7.1242785136570869E-2</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="3"/>
-        <v>3.1261141680936047</v>
+        <v>0.11889005590458053</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="3"/>
-        <v>2.9037223204941522</v>
+        <v>0.1619420163300512</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" si="3"/>
-        <v>2.7443815801507743</v>
+        <v>0.19950238581367652</v>
       </c>
       <c r="K29" s="3">
         <f t="shared" si="3"/>
-        <v>2.6237809632671794</v>
+        <v>0.23207908366935243</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="3"/>
-        <v>2.5288634512878163</v>
+        <v>0.260431580860643</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="3"/>
-        <v>2.4519392170299259</v>
+        <v>0.2852681345126698</v>
       </c>
       <c r="N29" s="3">
         <f t="shared" si="3"/>
-        <v>2.3881610866898644</v>
+        <v>0.30718228455437757</v>
       </c>
       <c r="O29" s="3">
         <f t="shared" si="3"/>
-        <v>2.3343098565187503</v>
+        <v>0.32665537635644037</v>
       </c>
       <c r="P29" s="3">
         <f t="shared" si="3"/>
-        <v>2.2881569845848695</v>
+        <v>0.34407461266106193</v>
       </c>
       <c r="Q29" s="3">
         <f t="shared" si="3"/>
-        <v>2.1819033207925971</v>
+        <v>0.38684639820852929</v>
       </c>
       <c r="R29" s="3">
         <f t="shared" si="3"/>
-        <v>2.0677140464123123</v>
+        <v>0.43719248115860782</v>
       </c>
       <c r="S29" s="3">
         <f t="shared" si="3"/>
-        <v>1.9943444645571398</v>
+        <v>0.47208532880176918</v>
       </c>
       <c r="T29" s="3">
         <f t="shared" si="2"/>
-        <v>1.9429159996941974</v>
+        <v>0.49779169996133549</v>
       </c>
       <c r="U29" s="3">
         <f t="shared" si="2"/>
-        <v>1.8751973768302734</v>
+        <v>0.53327719649989203</v>
       </c>
       <c r="V29" s="3">
         <f t="shared" si="2"/>
-        <v>1.8323832658781809</v>
+        <v>0.55670763333074258</v>
       </c>
       <c r="W29" s="3">
         <f t="shared" si="2"/>
-        <v>1.7405031649538241</v>
+        <v>0.60971647967950682</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
@@ -7994,79 +8023,79 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="1"/>
-        <v>5.340323217588069</v>
+        <v>9.9194823783766155E-4</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" si="3"/>
-        <v>3.9749308601386573</v>
+        <v>2.5330632141007624E-2</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" si="3"/>
-        <v>3.3901887803118527</v>
+        <v>7.1378044316401337E-2</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="3"/>
-        <v>3.0544149740526696</v>
+        <v>0.11932061057418998</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" si="3"/>
-        <v>2.8326540759914129</v>
+        <v>0.16277043108333872</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" si="3"/>
-        <v>2.6735549736905702</v>
+        <v>0.20078610578460676</v>
       </c>
       <c r="K30" s="3">
         <f t="shared" si="3"/>
-        <v>2.5529737072707168</v>
+        <v>0.23384658328373004</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" si="3"/>
-        <v>2.4579419812662113</v>
+        <v>0.26269360473517622</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" si="3"/>
-        <v>2.3808208872942513</v>
+        <v>0.28802465508614766</v>
       </c>
       <c r="N30" s="3">
         <f t="shared" si="3"/>
-        <v>2.3167941628727529</v>
+        <v>0.31042674651433921</v>
       </c>
       <c r="O30" s="3">
         <f t="shared" si="3"/>
-        <v>2.2626621724013427</v>
+        <v>0.33037731212157334</v>
       </c>
       <c r="P30" s="3">
         <f t="shared" si="3"/>
-        <v>2.2162091588117483</v>
+        <v>0.34826127871492846</v>
       </c>
       <c r="Q30" s="3">
         <f t="shared" si="3"/>
-        <v>2.109011570672652</v>
+        <v>0.39234150575897764</v>
       </c>
       <c r="R30" s="3">
         <f t="shared" si="3"/>
-        <v>1.9932944901521532</v>
+        <v>0.44458409719650333</v>
       </c>
       <c r="S30" s="3">
         <f t="shared" si="3"/>
-        <v>1.9185602258925087</v>
+        <v>0.48106559668934479</v>
       </c>
       <c r="T30" s="3">
         <f t="shared" si="2"/>
-        <v>1.8659402182574083</v>
+        <v>0.50811437466196152</v>
       </c>
       <c r="U30" s="3">
         <f t="shared" si="2"/>
-        <v>1.7962749927050046</v>
+        <v>0.54573735671000245</v>
       </c>
       <c r="V30" s="3">
         <f t="shared" si="2"/>
-        <v>1.751953309265075</v>
+        <v>0.57079146727916452</v>
       </c>
       <c r="W30" s="3">
         <f t="shared" si="2"/>
-        <v>1.6558490851696088</v>
+        <v>0.62826143247883126</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
@@ -8075,79 +8104,79 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785939049245053</v>
+        <v>9.8699654357073006E-4</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" si="3"/>
-        <v>3.8283669268710563</v>
+        <v>2.532421898033799E-2</v>
       </c>
       <c r="G31" s="3">
         <f t="shared" si="3"/>
-        <v>3.249618847516571</v>
+        <v>7.1652332138224251E-2</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="3"/>
-        <v>2.9165820135863965</v>
+        <v>0.12019997336212408</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" si="3"/>
-        <v>2.6960589580581265</v>
+        <v>0.16447370982902337</v>
       </c>
       <c r="J31" s="3">
         <f t="shared" si="3"/>
-        <v>2.5374031593431852</v>
+        <v>0.20344200562480083</v>
       </c>
       <c r="K31" s="3">
         <f t="shared" si="3"/>
-        <v>2.4168066612551917</v>
+        <v>0.23752479457676803</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" si="3"/>
-        <v>2.32148052290019</v>
+        <v>0.26742692578316485</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" si="3"/>
-        <v>2.2438894088550319</v>
+        <v>0.2938228811530173</v>
       </c>
       <c r="N31" s="3">
         <f t="shared" si="3"/>
-        <v>2.1792804082175317</v>
+        <v>0.31728525808569036</v>
       </c>
       <c r="O31" s="3">
         <f t="shared" si="3"/>
-        <v>2.1244943500855968</v>
+        <v>0.33828244501868154</v>
       </c>
       <c r="P31" s="3">
         <f t="shared" si="3"/>
-        <v>2.0773421947938573</v>
+        <v>0.35719374043239838</v>
       </c>
       <c r="Q31" s="3">
         <f t="shared" si="3"/>
-        <v>1.9679315561278719</v>
+        <v>0.40421278956761303</v>
       </c>
       <c r="R31" s="3">
         <f t="shared" si="3"/>
-        <v>1.84856071184281</v>
+        <v>0.46084121514479159</v>
       </c>
       <c r="S31" s="3">
         <f t="shared" si="3"/>
-        <v>1.770473228654909</v>
+        <v>0.50111927544455082</v>
       </c>
       <c r="T31" s="3">
         <f t="shared" si="2"/>
-        <v>1.7148488788501211</v>
+        <v>0.53147032401989502</v>
       </c>
       <c r="U31" s="3">
         <f t="shared" si="2"/>
-        <v>1.6401065631777625</v>
+        <v>0.57454649904444755</v>
       </c>
       <c r="V31" s="3">
         <f t="shared" si="2"/>
-        <v>1.5916940755927977</v>
+        <v>0.60391977080300774</v>
       </c>
       <c r="W31" s="3">
         <f t="shared" si="2"/>
-        <v>1.4832509898927291</v>
+        <v>0.674194729559777</v>
       </c>
     </row>
   </sheetData>
